--- a/outputs/daily/hr_rankings_2026-10-19_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-19_full.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>53.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.7</v>
+        <v>51.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>33.4</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1373,14 +1381,14 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>4</t>
@@ -1398,12 +1406,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1548,8 +1556,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1588,7 +1604,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1628,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.6</v>
+        <v>49.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1642,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1652,10 @@
         <v>33.4</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1649,14 +1665,14 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>3</t>
@@ -1674,12 +1690,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1824,8 +1840,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1839,24 +1863,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -1864,22 +1888,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1888,7 +1912,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.3</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,62 +1926,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1977,27 +1997,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2007,101 +2027,109 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2115,24 +2143,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -2140,22 +2168,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2164,7 +2192,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,40 +2206,40 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2226,12 +2254,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -2253,12 +2281,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2268,12 +2296,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2283,101 +2311,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2391,12 +2427,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2416,12 +2452,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2440,7 +2476,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,62 +2490,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2529,12 +2561,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2544,7 +2576,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2559,67 +2591,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2652,8 +2684,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2672,7 +2712,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,7 +2732,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2756,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.5</v>
+        <v>44.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2770,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2780,10 @@
         <v>31.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -2753,14 +2793,14 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>2</t>
@@ -2778,12 +2818,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -2928,8 +2968,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2968,7 +3016,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2992,7 +3040,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3054,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3064,10 @@
         <v>31.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3029,14 +3077,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>7</t>
@@ -3054,12 +3102,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -3204,8 +3252,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3244,7 +3300,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3324,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36.9</v>
+        <v>39.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3338,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3348,10 @@
         <v>33.4</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3305,14 +3361,14 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>6</t>
@@ -3330,12 +3386,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -3480,8 +3536,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3495,24 +3559,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -3520,22 +3584,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3544,7 +3608,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.9</v>
+        <v>38</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,62 +3622,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3633,12 +3693,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3648,12 +3708,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3663,101 +3723,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3771,24 +3839,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -3796,22 +3864,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3820,7 +3888,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.8</v>
+        <v>37.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,40 +3902,40 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3882,12 +3950,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -3909,27 +3977,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3939,101 +4007,109 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4072,7 +4148,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4172,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.3</v>
+        <v>34.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4186,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4196,10 @@
         <v>31.6</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4133,14 +4209,14 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>9</t>
@@ -4158,12 +4234,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -4308,8 +4384,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4323,12 +4407,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4348,7 +4432,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4456,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>34.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4470,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
         <v>32</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4461,12 +4541,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4476,12 +4556,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,67 +4571,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4584,8 +4664,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4599,24 +4687,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -4624,22 +4712,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4648,7 +4736,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.3</v>
+        <v>34.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,62 +4750,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4737,27 +4821,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,101 +4851,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4900,12 +4992,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4924,7 +5016,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.9</v>
+        <v>33.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,7 +5030,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -4948,10 +5040,10 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -4961,39 +5053,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5136,8 +5224,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5151,24 +5247,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -5176,22 +5272,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5200,7 +5296,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.8</v>
+        <v>32.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,40 +5310,40 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5262,12 +5358,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -5289,27 +5385,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5319,101 +5415,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5452,7 +5556,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5580,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.3</v>
+        <v>29.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,7 +5594,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5500,10 +5604,10 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5513,39 +5617,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5688,8 +5788,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6054,12 +6162,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6186,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>53.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6200,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6210,10 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6115,39 +6223,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6394,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6330,7 +6442,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6466,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6480,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6490,10 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6391,39 +6503,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6674,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6606,7 +6722,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6746,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.7</v>
+        <v>51.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6760,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6770,10 @@
         <v>33.4</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6667,14 +6783,14 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>4</t>
@@ -6692,12 +6808,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -6842,8 +6958,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6882,7 +7006,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +7030,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.6</v>
+        <v>49.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7044,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7054,10 @@
         <v>33.4</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -6943,14 +7067,14 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>3</t>
@@ -6968,12 +7092,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -7118,8 +7242,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7133,24 +7265,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -7158,22 +7290,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7182,7 +7314,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.3</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,62 +7328,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7271,27 +7399,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7301,101 +7429,109 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7409,24 +7545,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -7434,22 +7570,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7458,7 +7594,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,40 +7608,40 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7520,12 +7656,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -7547,12 +7683,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7562,12 +7698,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7577,101 +7713,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7685,12 +7829,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7710,12 +7854,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7734,7 +7878,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,62 +7892,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7823,12 +7963,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7838,7 +7978,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -7853,67 +7993,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -7946,8 +8086,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7966,7 +8114,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,7 +8134,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8158,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.5</v>
+        <v>44.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8172,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8182,10 @@
         <v>31.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -8047,14 +8195,14 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>2</t>
@@ -8072,12 +8220,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -8222,8 +8370,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8262,7 +8418,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8286,7 +8442,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8456,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8466,10 @@
         <v>31.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -8323,14 +8479,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>7</t>
@@ -8348,12 +8504,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -8498,8 +8654,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8538,7 +8702,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8726,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36.9</v>
+        <v>39.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8740,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8750,10 @@
         <v>33.4</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -8599,14 +8763,14 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>6</t>
@@ -8624,12 +8788,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -8774,8 +8938,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8789,24 +8961,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -8814,22 +8986,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -8838,7 +9010,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.9</v>
+        <v>38</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,62 +9024,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8927,12 +9095,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8942,12 +9110,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8957,101 +9125,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9065,24 +9241,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -9090,22 +9266,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9114,7 +9290,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.8</v>
+        <v>37.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,40 +9304,40 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -9176,12 +9352,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -9203,27 +9379,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9233,101 +9409,109 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9366,7 +9550,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9574,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.3</v>
+        <v>34.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9588,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9598,10 @@
         <v>31.6</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -9427,14 +9611,14 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>9</t>
@@ -9452,12 +9636,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -9602,8 +9786,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9617,12 +9809,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9642,7 +9834,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9858,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>34.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9872,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
         <v>32</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9755,12 +9943,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9770,12 +9958,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,67 +9973,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -9878,8 +10066,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9893,24 +10089,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -9918,22 +10114,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9942,7 +10138,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.3</v>
+        <v>34.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,62 +10152,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10031,27 +10223,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,101 +10253,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10194,12 +10394,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10218,7 +10418,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.9</v>
+        <v>33.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,7 +10432,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10242,10 +10442,10 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -10255,39 +10455,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10430,8 +10626,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10445,24 +10649,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -10470,22 +10674,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -10494,7 +10698,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.8</v>
+        <v>32.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,40 +10712,40 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -10556,12 +10760,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -10583,27 +10787,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10613,101 +10817,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10746,7 +10958,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10982,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.3</v>
+        <v>29.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,7 +10996,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10794,10 +11006,10 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10807,39 +11019,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10982,8 +11190,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>

--- a/outputs/daily/hr_rankings_2026-10-19_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-19_full.xlsx
@@ -1386,34 +1386,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1670,34 +1666,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2234,34 +2226,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2798,34 +2786,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3082,34 +3066,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3366,34 +3346,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3930,34 +3906,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4214,34 +4186,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5338,34 +5306,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6788,34 +6752,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7072,34 +7032,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7636,34 +7592,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8200,34 +8152,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8484,34 +8432,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8768,34 +8712,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -9332,34 +9272,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9616,34 +9552,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10740,34 +10672,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
